--- a/results/log_pv_cap/log_pv_cap_capacities_tests.xlsx
+++ b/results/log_pv_cap/log_pv_cap_capacities_tests.xlsx
@@ -451,27 +451,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83.41***</t>
+          <t>78.95***</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>38.25***</t>
+          <t>43.31***</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8419.93***</t>
+          <t>8108.28***</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>78.56***</t>
+          <t>68.21***</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>411.35***</t>
+          <t>399.04***</t>
         </is>
       </c>
     </row>
@@ -483,27 +483,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>83.41***</t>
+          <t>78.95***</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11.07***</t>
+          <t>12.06***</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7079.30***</t>
+          <t>6378.32***</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.33***</t>
+          <t>17.10***</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>411.35***</t>
+          <t>399.04***</t>
         </is>
       </c>
     </row>
@@ -515,27 +515,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>83.41***</t>
+          <t>78.95***</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10.14***</t>
+          <t>10.54***</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7059.60***</t>
+          <t>6343.92***</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13.17***</t>
+          <t>11.53***</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>411.35***</t>
+          <t>399.04***</t>
         </is>
       </c>
     </row>
